--- a/SCH-STH/Impact assessments/Mali/2025/sites.xlsx
+++ b/SCH-STH/Impact assessments/Mali/2025/sites.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Mali\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C4FA94-1855-4440-B021-C885FE4F0060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B81966D-9981-4500-91E1-FDDDB05E97BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E8DA33AE-561A-4783-8D75-88C284A879C6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="302">
   <si>
     <t>N°</t>
   </si>
@@ -942,6 +942,9 @@
   </si>
   <si>
     <t>Code ID</t>
+  </si>
+  <si>
+    <t>Code replacement</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1089,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1144,81 +1147,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1569,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02802C9A-C9ED-44E1-BBDB-EA690037CB45}">
-  <dimension ref="A1:R184"/>
+  <dimension ref="A1:S184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -1577,16 +1513,17 @@
     <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1608,29 +1545,32 @@
       <c r="G1" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="H1" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1652,29 +1592,33 @@
       <c r="G2">
         <v>101</v>
       </c>
-      <c r="I2" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="11" t="s">
+      <c r="H2" t="str">
+        <f>_xlfn.CONCAT(E2, " (", G2, ")")</f>
+        <v>ACHOURAT CENTRAL (101)</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1696,29 +1640,33 @@
       <c r="G3">
         <v>102</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H66" si="0">_xlfn.CONCAT(E3, " (", G3, ")")</f>
+        <v>AHEL AHMED OULAD SID ALI (102)</v>
+      </c>
+      <c r="J3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="O3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="P3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="R3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1740,26 +1688,30 @@
       <c r="G4">
         <v>103</v>
       </c>
-      <c r="K4" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="13" t="s">
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>OUDAIKA (103)</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="O4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="P4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="R4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1781,26 +1733,30 @@
       <c r="G5">
         <v>104</v>
       </c>
-      <c r="K5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="13" t="s">
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>HASSI OULD AHMED ALI (104)</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="O5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="P5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="R5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1822,26 +1778,30 @@
       <c r="G6">
         <v>105</v>
       </c>
-      <c r="K6" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" s="13" t="s">
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>HASSI DINA (105)</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="O6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="P6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="R6" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="R6" s="3" t="s">
+      <c r="S6" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1863,26 +1823,30 @@
       <c r="G7">
         <v>106</v>
       </c>
-      <c r="K7" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" s="13" t="s">
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>LAKERAJ (106)</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="O7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="P7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="R7" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="S7" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1904,26 +1868,30 @@
       <c r="G8">
         <v>107</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>TAGACHA (107)</v>
+      </c>
+      <c r="L8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="M8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="O8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="P8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="R8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1945,26 +1913,30 @@
       <c r="G9">
         <v>108</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>INKOMANE (108)</v>
+      </c>
+      <c r="L9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="M9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="O9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="12" t="s">
+      <c r="P9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="Q9" s="12" t="s">
+      <c r="R9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="S9" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1986,26 +1958,30 @@
       <c r="G10">
         <v>109</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>AL-MATLAA (109)</v>
+      </c>
+      <c r="L10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="M10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="13" t="s">
+      <c r="O10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="P10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="R10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2027,26 +2003,30 @@
       <c r="G11">
         <v>110</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>OULAD SLEIMANE 4 (110)</v>
+      </c>
+      <c r="L11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="M11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="O11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="P11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="Q11" s="12" t="s">
+      <c r="R11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="R11" s="3" t="s">
+      <c r="S11" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2068,26 +2048,30 @@
       <c r="G12">
         <v>111</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>AHEL ELBAYKIM (111)</v>
+      </c>
+      <c r="L12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="M12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="O12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="P12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="R12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="S12" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2109,26 +2093,30 @@
       <c r="G13">
         <v>112</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>IMBAKSA (112)</v>
+      </c>
+      <c r="L13" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="M13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="O13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="P13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="Q13" s="12" t="s">
+      <c r="R13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="R13" s="3" t="s">
+      <c r="S13" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2150,21 +2138,25 @@
       <c r="G14">
         <v>113</v>
       </c>
-      <c r="L14" s="19"/>
-      <c r="N14" s="11" t="s">
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>AHEL MOULAYE ZEINE (113)</v>
+      </c>
+      <c r="M14" s="19"/>
+      <c r="O14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="P14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="R14" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2186,20 +2178,24 @@
       <c r="G15">
         <v>114</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>TOURMOUZ 6 (114)</v>
+      </c>
+      <c r="O15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="O15" s="16" t="s">
+      <c r="P15" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="Q15" s="12" t="s">
+      <c r="R15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="S15" s="3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2221,20 +2217,24 @@
       <c r="G16">
         <v>115</v>
       </c>
-      <c r="N16" s="13" t="s">
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>TOUWAL (115)</v>
+      </c>
+      <c r="O16" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="P16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="R16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="R16" s="3" t="s">
+      <c r="S16" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2256,20 +2256,24 @@
       <c r="G17">
         <v>116</v>
       </c>
-      <c r="N17" s="13" t="s">
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v>AL-ATGA (116)</v>
+      </c>
+      <c r="O17" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="O17" s="16" t="s">
+      <c r="P17" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="Q17" s="12" t="s">
+      <c r="R17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="S17" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2291,20 +2295,24 @@
       <c r="G18">
         <v>117</v>
       </c>
-      <c r="N18" s="13" t="s">
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>NIBKIT-ELK (117)</v>
+      </c>
+      <c r="O18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="O18" s="15" t="s">
+      <c r="P18" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="Q18" s="11" t="s">
+      <c r="R18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="S18" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2326,20 +2334,24 @@
       <c r="G19">
         <v>118</v>
       </c>
-      <c r="N19" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O19" s="16" t="s">
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>AMACHACHAR (118)</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P19" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="Q19" s="12" t="s">
+      <c r="R19" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="R19" s="3" t="s">
+      <c r="S19" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2361,20 +2373,24 @@
       <c r="G20">
         <v>119</v>
       </c>
-      <c r="N20" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O20" s="15" t="s">
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v>AFFERNANE (119)</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P20" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="Q20" s="11" t="s">
+      <c r="R20" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="R20" s="5" t="s">
+      <c r="S20" s="5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2396,20 +2412,24 @@
       <c r="G21">
         <v>120</v>
       </c>
-      <c r="N21" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O21" s="16" t="s">
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v>AHEL HADAR (120)</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="Q21" s="12" t="s">
+      <c r="R21" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="R21" s="3" t="s">
+      <c r="S21" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2431,20 +2451,24 @@
       <c r="G22">
         <v>121</v>
       </c>
-      <c r="N22" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O22" s="15" t="s">
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v>HEL ACHEICH (121)</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P22" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="Q22" s="11" t="s">
+      <c r="R22" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="R22" s="3" t="s">
+      <c r="S22" s="3" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2466,20 +2490,24 @@
       <c r="G23">
         <v>122</v>
       </c>
-      <c r="N23" s="12" t="s">
-        <v>15</v>
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v>HASSI BATNA (122)</v>
       </c>
       <c r="O23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P23" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="Q23" s="12" t="s">
+      <c r="R23" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="R23" s="3" t="s">
+      <c r="S23" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2501,20 +2529,24 @@
       <c r="G24">
         <v>123</v>
       </c>
-      <c r="N24" s="11" t="s">
-        <v>15</v>
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v>ARAOUANE CENTRAL (123)</v>
       </c>
       <c r="O24" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="P24" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="Q24" s="11" t="s">
+      <c r="R24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="R24" s="3" t="s">
+      <c r="S24" s="3" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2536,20 +2568,24 @@
       <c r="G25">
         <v>124</v>
       </c>
-      <c r="N25" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O25" s="12" t="s">
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v>ALPHA-HOU (124)</v>
+      </c>
+      <c r="O25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P25" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="Q25" s="12" t="s">
+      <c r="R25" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="R25" s="3" t="s">
+      <c r="S25" s="3" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2571,20 +2607,24 @@
       <c r="G26">
         <v>125</v>
       </c>
-      <c r="N26" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O26" s="15" t="s">
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v>INKABAR (125)</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P26" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Q26" s="11" t="s">
+      <c r="R26" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="R26" s="3" t="s">
+      <c r="S26" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2606,20 +2646,24 @@
       <c r="G27">
         <v>126</v>
       </c>
-      <c r="N27" s="12" t="s">
-        <v>15</v>
+      <c r="H27" t="str">
+        <f t="shared" si="0"/>
+        <v>KEL ANTACHAG (126)</v>
       </c>
       <c r="O27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P27" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="Q27" s="12" t="s">
+      <c r="R27" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="R27" s="3" t="s">
+      <c r="S27" s="3" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2641,20 +2685,24 @@
       <c r="G28">
         <v>127</v>
       </c>
-      <c r="N28" s="11" t="s">
-        <v>15</v>
+      <c r="H28" t="str">
+        <f t="shared" si="0"/>
+        <v>BOU-DJEBEHA CENTRAL (127)</v>
       </c>
       <c r="O28" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="P28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="Q28" s="11" t="s">
+      <c r="R28" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="R28" s="3" t="s">
+      <c r="S28" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2676,20 +2724,24 @@
       <c r="G29">
         <v>128</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O29" s="16" t="s">
+      <c r="H29" t="str">
+        <f t="shared" si="0"/>
+        <v>FRACTION BOUJBEHA SIDI AHMED (128)</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P29" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="Q29" s="12" t="s">
+      <c r="R29" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="R29" s="3" t="s">
+      <c r="S29" s="3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2711,20 +2763,24 @@
       <c r="G30">
         <v>129</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O30" s="11" t="s">
+      <c r="H30" t="str">
+        <f t="shared" si="0"/>
+        <v>LICHYA (129)</v>
+      </c>
+      <c r="O30" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P30" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="Q30" s="11" t="s">
+      <c r="R30" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="R30" s="3" t="s">
+      <c r="S30" s="3" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2746,20 +2802,24 @@
       <c r="G31">
         <v>130</v>
       </c>
-      <c r="N31" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O31" s="12" t="s">
+      <c r="H31" t="str">
+        <f t="shared" si="0"/>
+        <v>KOUNTA 2 (130)</v>
+      </c>
+      <c r="O31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P31" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="Q31" s="12" t="s">
+      <c r="R31" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="R31" s="3" t="s">
+      <c r="S31" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2781,20 +2841,24 @@
       <c r="G32">
         <v>131</v>
       </c>
-      <c r="N32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O32" s="11" t="s">
+      <c r="H32" t="str">
+        <f t="shared" si="0"/>
+        <v>TICHIFT (131)</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P32" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="Q32" s="11" t="s">
+      <c r="R32" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="R32" s="3" t="s">
+      <c r="S32" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2816,20 +2880,24 @@
       <c r="G33">
         <v>132</v>
       </c>
-      <c r="N33" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="O33" s="16" t="s">
+      <c r="H33" t="str">
+        <f t="shared" si="0"/>
+        <v>SIDI ALAMINE (132)</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P33" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="Q33" s="12" t="s">
+      <c r="R33" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="R33" s="3" t="s">
+      <c r="S33" s="3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2851,20 +2919,24 @@
       <c r="G34">
         <v>133</v>
       </c>
-      <c r="N34" s="11" t="s">
-        <v>15</v>
+      <c r="H34" t="str">
+        <f t="shared" si="0"/>
+        <v>FOUM-ALBA CENTRAL (133)</v>
       </c>
       <c r="O34" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="P34" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="Q34" s="11" t="s">
+      <c r="R34" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="R34" s="3" t="s">
+      <c r="S34" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2886,20 +2958,24 @@
       <c r="G35">
         <v>134</v>
       </c>
-      <c r="N35" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="O35" s="12" t="s">
+      <c r="H35" t="str">
+        <f t="shared" si="0"/>
+        <v>OULAD BOUHINDA I (134)</v>
+      </c>
+      <c r="O35" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="P35" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="12" t="s">
+      <c r="R35" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="R35" s="3" t="s">
+      <c r="S35" s="3" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2921,20 +2997,24 @@
       <c r="G36">
         <v>135</v>
       </c>
-      <c r="N36" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O36" s="5" t="s">
+      <c r="H36" t="str">
+        <f t="shared" si="0"/>
+        <v>OULAD ICH VI (135)</v>
+      </c>
+      <c r="O36" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="P36" s="5" t="s">
         <v>298</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="R36" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S36" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2956,20 +3036,24 @@
       <c r="G37">
         <v>136</v>
       </c>
-      <c r="N37" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O37" s="5" t="s">
+      <c r="H37" t="str">
+        <f t="shared" si="0"/>
+        <v>OULAD AMRANE 2 (136)</v>
+      </c>
+      <c r="O37" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P37" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="R37" s="3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S37" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2991,20 +3075,24 @@
       <c r="G38">
         <v>137</v>
       </c>
-      <c r="N38" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O38" s="3" t="s">
+      <c r="H38" t="str">
+        <f t="shared" si="0"/>
+        <v>OULAD ALAD GOUWANINE BLANCH (137)</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P38" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="Q38" s="5" t="s">
+      <c r="R38" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="R38" s="5" t="s">
+      <c r="S38" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3026,20 +3114,24 @@
       <c r="G39">
         <v>138</v>
       </c>
-      <c r="N39" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O39" s="3" t="s">
+      <c r="H39" t="str">
+        <f t="shared" si="0"/>
+        <v>AKIZIME II (138)</v>
+      </c>
+      <c r="O39" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P39" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Q39" s="3" t="s">
+      <c r="R39" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="R39" s="3" t="s">
+      <c r="S39" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3061,20 +3153,24 @@
       <c r="G40">
         <v>139</v>
       </c>
-      <c r="N40" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O40" s="3" t="s">
+      <c r="H40" t="str">
+        <f t="shared" si="0"/>
+        <v>ZOUEYA (139)</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P40" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Q40" s="3" t="s">
+      <c r="R40" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="R40" s="3" t="s">
+      <c r="S40" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3096,20 +3192,24 @@
       <c r="G41">
         <v>140</v>
       </c>
-      <c r="N41" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="O41" s="3" t="s">
+      <c r="H41" t="str">
+        <f t="shared" si="0"/>
+        <v>OULAD OUMRAN 7 (140)</v>
+      </c>
+      <c r="O41" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="P41" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q41" s="3" t="s">
+      <c r="R41" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="R41" s="3" t="s">
+      <c r="S41" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14">
         <v>1</v>
       </c>
@@ -3131,20 +3231,24 @@
       <c r="G42">
         <v>141</v>
       </c>
-      <c r="N42" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="O42" s="3" t="s">
+      <c r="H42" t="str">
+        <f t="shared" si="0"/>
+        <v>AOUROU (141)</v>
+      </c>
+      <c r="O42" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="P42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Q42" s="5" t="s">
+      <c r="R42" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="R42" s="3" t="s">
+      <c r="S42" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>2</v>
       </c>
@@ -3166,20 +3270,24 @@
       <c r="G43">
         <v>142</v>
       </c>
-      <c r="N43" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O43" s="3" t="s">
+      <c r="H43" t="str">
+        <f t="shared" si="0"/>
+        <v>SELEKETE GAGNY (142)</v>
+      </c>
+      <c r="O43" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P43" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q43" s="3" t="s">
+      <c r="R43" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="R43" s="3" t="s">
+      <c r="S43" s="3" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>3</v>
       </c>
@@ -3201,20 +3309,24 @@
       <c r="G44">
         <v>143</v>
       </c>
-      <c r="N44" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O44" s="5" t="s">
+      <c r="H44" t="str">
+        <f t="shared" si="0"/>
+        <v>SOKOURANI (143)</v>
+      </c>
+      <c r="O44" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P44" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S44" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14">
         <v>4</v>
       </c>
@@ -3236,20 +3348,24 @@
       <c r="G45">
         <v>144</v>
       </c>
-      <c r="N45" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O45" s="3" t="s">
+      <c r="H45" t="str">
+        <f t="shared" si="0"/>
+        <v>DIGUIDIAN GOPELA (144)</v>
+      </c>
+      <c r="O45" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P45" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Q45" s="3" t="s">
+      <c r="R45" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="R45" s="3" t="s">
+      <c r="S45" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -3271,20 +3387,24 @@
       <c r="G46">
         <v>145</v>
       </c>
-      <c r="N46" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O46" s="3" t="s">
+      <c r="H46" t="str">
+        <f t="shared" si="0"/>
+        <v>HAMDALLAYE (BATAMA) (145)</v>
+      </c>
+      <c r="O46" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P46" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="Q46" s="3" t="s">
+      <c r="R46" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="R46" s="3" t="s">
+      <c r="S46" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -3306,20 +3426,24 @@
       <c r="G47">
         <v>146</v>
       </c>
-      <c r="N47" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O47" s="3" t="s">
+      <c r="H47" t="str">
+        <f t="shared" si="0"/>
+        <v>BENCOUNDA (146)</v>
+      </c>
+      <c r="O47" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P47" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Q47" s="3" t="s">
+      <c r="R47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="R47" s="5" t="s">
+      <c r="S47" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14">
         <v>7</v>
       </c>
@@ -3341,20 +3465,24 @@
       <c r="G48">
         <v>147</v>
       </c>
-      <c r="N48" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O48" s="5" t="s">
+      <c r="H48" t="str">
+        <f t="shared" si="0"/>
+        <v>DIYALA KHASSO (147)</v>
+      </c>
+      <c r="O48" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P48" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="Q48" s="3" t="s">
+      <c r="R48" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="R48" s="3" t="s">
+      <c r="S48" s="3" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>8</v>
       </c>
@@ -3376,20 +3504,24 @@
       <c r="G49">
         <v>148</v>
       </c>
-      <c r="N49" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O49" s="3" t="s">
+      <c r="H49" t="str">
+        <f t="shared" si="0"/>
+        <v>BANAYA (148)</v>
+      </c>
+      <c r="O49" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P49" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Q49" s="3" t="s">
+      <c r="R49" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="R49" s="3" t="s">
+      <c r="S49" s="3" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>9</v>
       </c>
@@ -3411,20 +3543,24 @@
       <c r="G50">
         <v>149</v>
       </c>
-      <c r="N50" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O50" s="3" t="s">
+      <c r="H50" t="str">
+        <f t="shared" si="0"/>
+        <v>BOUROUKOUN (149)</v>
+      </c>
+      <c r="O50" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P50" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="Q50" s="5" t="s">
+      <c r="R50" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="R50" s="3" t="s">
+      <c r="S50" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14">
         <v>10</v>
       </c>
@@ -3446,20 +3582,24 @@
       <c r="G51">
         <v>150</v>
       </c>
-      <c r="N51" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O51" s="3" t="s">
+      <c r="H51" t="str">
+        <f t="shared" si="0"/>
+        <v>DIABOUGOU (DIBOLI) (150)</v>
+      </c>
+      <c r="O51" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P51" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="Q51" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="R51" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S51" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>11</v>
       </c>
@@ -3481,20 +3621,24 @@
       <c r="G52">
         <v>151</v>
       </c>
-      <c r="N52" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O52" s="5" t="s">
+      <c r="H52" t="str">
+        <f t="shared" si="0"/>
+        <v>DRAMANÉ (151)</v>
+      </c>
+      <c r="O52" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P52" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="Q52" s="3" t="s">
+      <c r="R52" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="R52" s="3" t="s">
+      <c r="S52" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>12</v>
       </c>
@@ -3516,20 +3660,24 @@
       <c r="G53">
         <v>152</v>
       </c>
-      <c r="N53" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O53" s="3" t="s">
+      <c r="H53" t="str">
+        <f t="shared" si="0"/>
+        <v>TISSI GANSOYE (152)</v>
+      </c>
+      <c r="O53" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P53" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="Q53" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="R53" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S53" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14">
         <v>13</v>
       </c>
@@ -3551,20 +3699,24 @@
       <c r="G54">
         <v>153</v>
       </c>
-      <c r="N54" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O54" s="3" t="s">
+      <c r="H54" t="str">
+        <f t="shared" si="0"/>
+        <v>SANGARA (153)</v>
+      </c>
+      <c r="O54" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P54" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="Q54" s="3" t="s">
+      <c r="R54" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="R54" s="3" t="s">
+      <c r="S54" s="3" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>14</v>
       </c>
@@ -3586,20 +3738,24 @@
       <c r="G55">
         <v>154</v>
       </c>
-      <c r="N55" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O55" s="3" t="s">
+      <c r="H55" t="str">
+        <f t="shared" si="0"/>
+        <v>KOTERA (154)</v>
+      </c>
+      <c r="O55" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P55" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="Q55" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="R55" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S55" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>15</v>
       </c>
@@ -3621,20 +3777,24 @@
       <c r="G56">
         <v>155</v>
       </c>
-      <c r="N56" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O56" s="3" t="s">
+      <c r="H56" t="str">
+        <f t="shared" si="0"/>
+        <v>WAIGUILOU (155)</v>
+      </c>
+      <c r="O56" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P56" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q56" s="3" t="s">
+      <c r="R56" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="R56" s="3" t="s">
+      <c r="S56" s="3" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14">
         <v>16</v>
       </c>
@@ -3656,20 +3816,24 @@
       <c r="G57">
         <v>156</v>
       </c>
-      <c r="N57" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O57" s="3" t="s">
+      <c r="H57" t="str">
+        <f t="shared" si="0"/>
+        <v>PAPARA (156)</v>
+      </c>
+      <c r="O57" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P57" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="Q57" s="5" t="s">
+      <c r="R57" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="R57" s="3" t="s">
+      <c r="S57" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>17</v>
       </c>
@@ -3691,20 +3855,24 @@
       <c r="G58">
         <v>157</v>
       </c>
-      <c r="N58" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O58" s="3" t="s">
+      <c r="H58" t="str">
+        <f t="shared" si="0"/>
+        <v>KONIAKARI (157)</v>
+      </c>
+      <c r="O58" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="Q58" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="R58" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S58" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>18</v>
       </c>
@@ -3726,20 +3894,24 @@
       <c r="G59">
         <v>158</v>
       </c>
-      <c r="N59" s="13" t="s">
+      <c r="H59" t="str">
+        <f t="shared" si="0"/>
+        <v>SOUTOUKOULÉ (158)</v>
+      </c>
+      <c r="O59" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O59" s="3" t="s">
+      <c r="P59" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q59" s="3" t="s">
+      <c r="R59" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="R59" s="3" t="s">
+      <c r="S59" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14">
         <v>19</v>
       </c>
@@ -3761,20 +3933,24 @@
       <c r="G60">
         <v>159</v>
       </c>
-      <c r="N60" s="13" t="s">
+      <c r="H60" t="str">
+        <f t="shared" si="0"/>
+        <v>SEYE BOULE (159)</v>
+      </c>
+      <c r="O60" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O60" s="3" t="s">
+      <c r="P60" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="Q60" s="3" t="s">
+      <c r="R60" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="R60" s="3" t="s">
+      <c r="S60" s="3" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>20</v>
       </c>
@@ -3796,20 +3972,24 @@
       <c r="G61">
         <v>160</v>
       </c>
-      <c r="N61" s="13" t="s">
+      <c r="H61" t="str">
+        <f t="shared" si="0"/>
+        <v>BANKAMÉ (160)</v>
+      </c>
+      <c r="O61" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O61" s="3" t="s">
+      <c r="P61" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="Q61" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="R61" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S61" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>21</v>
       </c>
@@ -3831,20 +4011,24 @@
       <c r="G62">
         <v>161</v>
       </c>
-      <c r="N62" s="13" t="s">
+      <c r="H62" t="str">
+        <f t="shared" si="0"/>
+        <v>LAFIABOUGOU (161)</v>
+      </c>
+      <c r="O62" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O62" s="3" t="s">
+      <c r="P62" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S62" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="14">
         <v>22</v>
       </c>
@@ -3866,20 +4050,24 @@
       <c r="G63">
         <v>162</v>
       </c>
-      <c r="N63" s="13" t="s">
+      <c r="H63" t="str">
+        <f t="shared" si="0"/>
+        <v>LAFIABOUGOU SUD (162)</v>
+      </c>
+      <c r="O63" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O63" s="3" t="s">
+      <c r="P63" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Q63" s="3" t="s">
+      <c r="R63" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="R63" s="3" t="s">
+      <c r="S63" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>23</v>
       </c>
@@ -3901,20 +4089,24 @@
       <c r="G64">
         <v>163</v>
       </c>
-      <c r="N64" s="13" t="s">
+      <c r="H64" t="str">
+        <f t="shared" si="0"/>
+        <v>LAKAFIA (163)</v>
+      </c>
+      <c r="O64" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O64" s="3" t="s">
+      <c r="P64" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="Q64" s="3" t="s">
+      <c r="R64" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="R64" s="3" t="s">
+      <c r="S64" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>24</v>
       </c>
@@ -3936,20 +4128,24 @@
       <c r="G65">
         <v>164</v>
       </c>
-      <c r="N65" s="13" t="s">
+      <c r="H65" t="str">
+        <f t="shared" si="0"/>
+        <v>LÉYA (164)</v>
+      </c>
+      <c r="O65" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O65" s="3" t="s">
+      <c r="P65" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q65" s="3" t="s">
+      <c r="R65" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="R65" s="3" t="s">
+      <c r="S65" s="3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="14">
         <v>25</v>
       </c>
@@ -3971,20 +4167,24 @@
       <c r="G66">
         <v>165</v>
       </c>
-      <c r="N66" s="13" t="s">
+      <c r="H66" t="str">
+        <f t="shared" si="0"/>
+        <v>SALAMOU (165)</v>
+      </c>
+      <c r="O66" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O66" s="3" t="s">
+      <c r="P66" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="Q66" s="5" t="s">
+      <c r="R66" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="R66" s="3" t="s">
+      <c r="S66" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>26</v>
       </c>
@@ -4006,20 +4206,24 @@
       <c r="G67">
         <v>166</v>
       </c>
-      <c r="N67" s="13" t="s">
+      <c r="H67" t="str">
+        <f t="shared" ref="H67:H130" si="1">_xlfn.CONCAT(E67, " (", G67, ")")</f>
+        <v>MOULINÉ (166)</v>
+      </c>
+      <c r="O67" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O67" s="3" t="s">
+      <c r="P67" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="Q67" s="5" t="s">
+      <c r="R67" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="R67" s="3" t="s">
+      <c r="S67" s="3" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>27</v>
       </c>
@@ -4041,20 +4245,24 @@
       <c r="G68">
         <v>167</v>
       </c>
-      <c r="N68" s="13" t="s">
+      <c r="H68" t="str">
+        <f t="shared" si="1"/>
+        <v>TAFACIRGA DIOMBOUGOU (167)</v>
+      </c>
+      <c r="O68" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O68" s="3" t="s">
+      <c r="P68" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="Q68" s="3" t="s">
+      <c r="R68" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R68" s="3" t="s">
+      <c r="S68" s="3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="14">
         <v>28</v>
       </c>
@@ -4076,20 +4284,24 @@
       <c r="G69">
         <v>168</v>
       </c>
-      <c r="N69" s="13" t="s">
+      <c r="H69" t="str">
+        <f t="shared" si="1"/>
+        <v>PLATEAU (168)</v>
+      </c>
+      <c r="O69" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O69" s="3" t="s">
+      <c r="P69" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q69" s="3" t="s">
+      <c r="R69" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R69" s="3" t="s">
+      <c r="S69" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>29</v>
       </c>
@@ -4111,20 +4323,24 @@
       <c r="G70">
         <v>169</v>
       </c>
-      <c r="N70" s="13" t="s">
+      <c r="H70" t="str">
+        <f t="shared" si="1"/>
+        <v>KANTELA (169)</v>
+      </c>
+      <c r="O70" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O70" s="3" t="s">
+      <c r="P70" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q70" s="5" t="s">
+      <c r="R70" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="R70" s="3" t="s">
+      <c r="S70" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>30</v>
       </c>
@@ -4146,20 +4362,24 @@
       <c r="G71">
         <v>170</v>
       </c>
-      <c r="N71" s="13" t="s">
+      <c r="H71" t="str">
+        <f t="shared" si="1"/>
+        <v>YATÉLA (170)</v>
+      </c>
+      <c r="O71" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O71" s="3" t="s">
+      <c r="P71" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="Q71" s="3" t="s">
+      <c r="R71" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="R71" s="3" t="s">
+      <c r="S71" s="3" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="14">
         <v>31</v>
       </c>
@@ -4181,20 +4401,24 @@
       <c r="G72">
         <v>171</v>
       </c>
-      <c r="N72" s="13" t="s">
+      <c r="H72" t="str">
+        <f t="shared" si="1"/>
+        <v>KALAO (171)</v>
+      </c>
+      <c r="O72" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O72" s="3" t="s">
+      <c r="P72" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S72" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>32</v>
       </c>
@@ -4216,20 +4440,24 @@
       <c r="G73">
         <v>172</v>
       </c>
-      <c r="N73" s="13" t="s">
+      <c r="H73" t="str">
+        <f t="shared" si="1"/>
+        <v>KANDIA (172)</v>
+      </c>
+      <c r="O73" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O73" s="3" t="s">
+      <c r="P73" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="Q73" s="5" t="s">
+      <c r="R73" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="R73" s="5" t="s">
+      <c r="S73" s="5" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>33</v>
       </c>
@@ -4251,20 +4479,24 @@
       <c r="G74">
         <v>173</v>
       </c>
-      <c r="N74" s="13" t="s">
+      <c r="H74" t="str">
+        <f t="shared" si="1"/>
+        <v>TAFASSIRGA (173)</v>
+      </c>
+      <c r="O74" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O74" s="3" t="s">
+      <c r="P74" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q74" s="3" t="s">
+      <c r="R74" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="R74" s="5" t="s">
+      <c r="S74" s="5" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="14">
         <v>34</v>
       </c>
@@ -4286,20 +4518,24 @@
       <c r="G75">
         <v>174</v>
       </c>
-      <c r="N75" s="13" t="s">
+      <c r="H75" t="str">
+        <f t="shared" si="1"/>
+        <v>SOUÉNA GANDEGA (174)</v>
+      </c>
+      <c r="O75" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O75" s="3" t="s">
+      <c r="P75" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="Q75" s="5" t="s">
+      <c r="R75" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="R75" s="5" t="s">
+      <c r="S75" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>35</v>
       </c>
@@ -4321,20 +4557,24 @@
       <c r="G76">
         <v>175</v>
       </c>
-      <c r="N76" s="13" t="s">
+      <c r="H76" t="str">
+        <f t="shared" si="1"/>
+        <v>FEGUI (175)</v>
+      </c>
+      <c r="O76" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O76" s="3" t="s">
+      <c r="P76" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Q76" s="3" t="s">
+      <c r="R76" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="R76" s="3" t="s">
+      <c r="S76" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>36</v>
       </c>
@@ -4356,20 +4596,24 @@
       <c r="G77">
         <v>176</v>
       </c>
-      <c r="N77" s="13" t="s">
+      <c r="H77" t="str">
+        <f t="shared" si="1"/>
+        <v>BREAMASSOU (176)</v>
+      </c>
+      <c r="O77" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O77" s="3" t="s">
+      <c r="P77" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="Q77" s="3" t="s">
+      <c r="R77" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="R77" s="3" t="s">
+      <c r="S77" s="3" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="14">
         <v>37</v>
       </c>
@@ -4391,20 +4635,24 @@
       <c r="G78">
         <v>177</v>
       </c>
-      <c r="N78" s="13" t="s">
+      <c r="H78" t="str">
+        <f t="shared" si="1"/>
+        <v>TABACO (177)</v>
+      </c>
+      <c r="O78" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O78" s="3" t="s">
+      <c r="P78" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q78" s="3" t="s">
+      <c r="R78" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="R78" s="3" t="s">
+      <c r="S78" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>38</v>
       </c>
@@ -4426,20 +4674,24 @@
       <c r="G79">
         <v>178</v>
       </c>
-      <c r="N79" s="13" t="s">
+      <c r="H79" t="str">
+        <f t="shared" si="1"/>
+        <v>KOUMBINÉ/DARALAM (178)</v>
+      </c>
+      <c r="O79" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O79" s="3" t="s">
+      <c r="P79" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="Q79" s="3" t="s">
+      <c r="R79" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="R79" s="3" t="s">
+      <c r="S79" s="3" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>39</v>
       </c>
@@ -4461,20 +4713,24 @@
       <c r="G80">
         <v>179</v>
       </c>
-      <c r="N80" s="13" t="s">
+      <c r="H80" t="str">
+        <f t="shared" si="1"/>
+        <v>SALAMOU (NAYELA) (179)</v>
+      </c>
+      <c r="O80" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O80" s="3" t="s">
+      <c r="P80" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="Q80" s="3" t="s">
+      <c r="R80" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="R80" s="3" t="s">
+      <c r="S80" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="14">
         <v>40</v>
       </c>
@@ -4496,20 +4752,24 @@
       <c r="G81">
         <v>180</v>
       </c>
-      <c r="N81" s="12" t="s">
+      <c r="H81" t="str">
+        <f t="shared" si="1"/>
+        <v>SERENATY (180)</v>
+      </c>
+      <c r="O81" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="O81" s="3" t="s">
+      <c r="P81" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S81" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="14">
         <v>41</v>
       </c>
@@ -4531,20 +4791,24 @@
       <c r="G82">
         <v>181</v>
       </c>
-      <c r="N82" s="11" t="s">
+      <c r="H82" t="str">
+        <f t="shared" si="1"/>
+        <v>BAYE (181)</v>
+      </c>
+      <c r="O82" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O82" s="3" t="s">
+      <c r="P82" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="Q82" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="R82" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S82" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="14">
         <v>42</v>
       </c>
@@ -4566,20 +4830,24 @@
       <c r="G83">
         <v>182</v>
       </c>
-      <c r="N83" s="13" t="s">
+      <c r="H83" t="str">
+        <f t="shared" si="1"/>
+        <v>MAMBA (182)</v>
+      </c>
+      <c r="O83" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="Q83" s="3" t="s">
+      <c r="R83" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="R83" s="3" t="s">
+      <c r="S83" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="14">
         <v>43</v>
       </c>
@@ -4601,20 +4869,24 @@
       <c r="G84">
         <v>183</v>
       </c>
-      <c r="N84" s="13" t="s">
+      <c r="H84" t="str">
+        <f t="shared" si="1"/>
+        <v>BINEA (183)</v>
+      </c>
+      <c r="O84" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O84" s="3" t="s">
+      <c r="P84" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="Q84" s="3" t="s">
+      <c r="R84" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="R84" s="3" t="s">
+      <c r="S84" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="14">
         <v>44</v>
       </c>
@@ -4636,20 +4908,24 @@
       <c r="G85">
         <v>184</v>
       </c>
-      <c r="N85" s="13" t="s">
+      <c r="H85" t="str">
+        <f t="shared" si="1"/>
+        <v>DARSALAMII (184)</v>
+      </c>
+      <c r="O85" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O85" s="3" t="s">
+      <c r="P85" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="Q85" s="3" t="s">
+      <c r="R85" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="R85" s="3" t="s">
+      <c r="S85" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="14">
         <v>45</v>
       </c>
@@ -4671,20 +4947,24 @@
       <c r="G86">
         <v>185</v>
       </c>
-      <c r="N86" s="13" t="s">
+      <c r="H86" t="str">
+        <f t="shared" si="1"/>
+        <v>KOUKA (185)</v>
+      </c>
+      <c r="O86" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O86" s="3" t="s">
+      <c r="P86" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="Q86" s="3" t="s">
+      <c r="R86" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="R86" s="3" t="s">
+      <c r="S86" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="14">
         <v>46</v>
       </c>
@@ -4706,20 +4986,24 @@
       <c r="G87">
         <v>186</v>
       </c>
-      <c r="N87" s="13" t="s">
+      <c r="H87" t="str">
+        <f t="shared" si="1"/>
+        <v>SIRIBAYA (186)</v>
+      </c>
+      <c r="O87" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O87" s="5" t="s">
+      <c r="P87" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="Q87" s="5" t="s">
+      <c r="R87" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="R87" s="5" t="s">
+      <c r="S87" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="14">
         <v>47</v>
       </c>
@@ -4741,20 +5025,24 @@
       <c r="G88">
         <v>187</v>
       </c>
-      <c r="N88" s="13" t="s">
+      <c r="H88" t="str">
+        <f t="shared" si="1"/>
+        <v>FARABA (187)</v>
+      </c>
+      <c r="O88" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O88" s="3" t="s">
+      <c r="P88" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Q88" s="3" t="s">
+      <c r="R88" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R88" s="3" t="s">
+      <c r="S88" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="14">
         <v>48</v>
       </c>
@@ -4776,20 +5064,24 @@
       <c r="G89">
         <v>188</v>
       </c>
-      <c r="N89" s="13" t="s">
+      <c r="H89" t="str">
+        <f t="shared" si="1"/>
+        <v>SITAKOTO DINDERA (188)</v>
+      </c>
+      <c r="O89" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O89" s="3" t="s">
+      <c r="P89" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="Q89" s="3" t="s">
+      <c r="R89" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="R89" s="3" t="s">
+      <c r="S89" s="3" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="14">
         <v>49</v>
       </c>
@@ -4811,20 +5103,24 @@
       <c r="G90">
         <v>189</v>
       </c>
-      <c r="N90" s="13" t="s">
+      <c r="H90" t="str">
+        <f t="shared" si="1"/>
+        <v>TOUMBOUN (189)</v>
+      </c>
+      <c r="O90" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O90" s="3" t="s">
+      <c r="P90" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="Q90" s="5" t="s">
+      <c r="R90" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="R90" s="3" t="s">
+      <c r="S90" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="14">
         <v>50</v>
       </c>
@@ -4846,20 +5142,24 @@
       <c r="G91">
         <v>190</v>
       </c>
-      <c r="N91" s="13" t="s">
+      <c r="H91" t="str">
+        <f t="shared" si="1"/>
+        <v>DIOULAFOUNDOUBA (190)</v>
+      </c>
+      <c r="O91" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O91" s="3" t="s">
+      <c r="P91" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="Q91" s="3" t="s">
+      <c r="R91" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="R91" s="3" t="s">
+      <c r="S91" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="14">
         <v>51</v>
       </c>
@@ -4881,20 +5181,24 @@
       <c r="G92">
         <v>191</v>
       </c>
-      <c r="N92" s="13" t="s">
+      <c r="H92" t="str">
+        <f t="shared" si="1"/>
+        <v>KOUFARA (191)</v>
+      </c>
+      <c r="O92" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O92" s="3" t="s">
+      <c r="P92" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="Q92" s="3" t="s">
+      <c r="R92" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="R92" s="3" t="s">
+      <c r="S92" s="3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="14">
         <v>52</v>
       </c>
@@ -4916,20 +5220,24 @@
       <c r="G93">
         <v>192</v>
       </c>
-      <c r="N93" s="13" t="s">
+      <c r="H93" t="str">
+        <f t="shared" si="1"/>
+        <v>MOGOYAFARA (192)</v>
+      </c>
+      <c r="O93" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O93" s="3" t="s">
+      <c r="P93" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="Q93" s="3" t="s">
+      <c r="R93" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="R93" s="3" t="s">
+      <c r="S93" s="3" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="14">
         <v>53</v>
       </c>
@@ -4951,20 +5259,24 @@
       <c r="G94">
         <v>193</v>
       </c>
-      <c r="N94" s="13" t="s">
+      <c r="H94" t="str">
+        <f t="shared" si="1"/>
+        <v>KOLOMBA II (193)</v>
+      </c>
+      <c r="O94" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="Q94" s="3" t="s">
+      <c r="R94" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="R94" s="3" t="s">
+      <c r="S94" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="14">
         <v>54</v>
       </c>
@@ -4986,20 +5298,24 @@
       <c r="G95">
         <v>194</v>
       </c>
-      <c r="N95" s="13" t="s">
+      <c r="H95" t="str">
+        <f t="shared" si="1"/>
+        <v>DIRE-KEBALE (194)</v>
+      </c>
+      <c r="O95" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O95" s="3" t="s">
+      <c r="P95" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="Q95" s="3" t="s">
+      <c r="R95" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="R95" s="3" t="s">
+      <c r="S95" s="3" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="14">
         <v>55</v>
       </c>
@@ -5021,20 +5337,24 @@
       <c r="G96">
         <v>195</v>
       </c>
-      <c r="N96" s="13" t="s">
+      <c r="H96" t="str">
+        <f t="shared" si="1"/>
+        <v>DARO (195)</v>
+      </c>
+      <c r="O96" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q96" s="3" t="s">
+      <c r="R96" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="R96" s="3" t="s">
+      <c r="S96" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="14">
         <v>56</v>
       </c>
@@ -5056,20 +5376,24 @@
       <c r="G97">
         <v>196</v>
       </c>
-      <c r="N97" s="13" t="s">
+      <c r="H97" t="str">
+        <f t="shared" si="1"/>
+        <v>TABACOTO (196)</v>
+      </c>
+      <c r="O97" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O97" s="3" t="s">
+      <c r="P97" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="Q97" s="5" t="s">
+      <c r="R97" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="R97" s="5" t="s">
+      <c r="S97" s="5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="14">
         <v>57</v>
       </c>
@@ -5091,20 +5415,24 @@
       <c r="G98">
         <v>197</v>
       </c>
-      <c r="N98" s="13" t="s">
+      <c r="H98" t="str">
+        <f t="shared" si="1"/>
+        <v>KOUROUBODALA (197)</v>
+      </c>
+      <c r="O98" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O98" s="3" t="s">
+      <c r="P98" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="Q98" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="R98" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S98" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="14">
         <v>58</v>
       </c>
@@ -5126,20 +5454,24 @@
       <c r="G99">
         <v>198</v>
       </c>
-      <c r="N99" s="13" t="s">
+      <c r="H99" t="str">
+        <f t="shared" si="1"/>
+        <v>TINTIMBA (198)</v>
+      </c>
+      <c r="O99" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O99" s="3" t="s">
+      <c r="P99" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="Q99" s="3" t="s">
+      <c r="R99" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="R99" s="5" t="s">
+      <c r="S99" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="14">
         <v>59</v>
       </c>
@@ -5161,20 +5493,24 @@
       <c r="G100">
         <v>199</v>
       </c>
-      <c r="N100" s="13" t="s">
+      <c r="H100" t="str">
+        <f t="shared" si="1"/>
+        <v>SITAFETO (199)</v>
+      </c>
+      <c r="O100" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S100" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="14">
         <v>60</v>
       </c>
@@ -5196,20 +5532,24 @@
       <c r="G101">
         <v>200</v>
       </c>
-      <c r="N101" s="12" t="s">
+      <c r="H101" t="str">
+        <f t="shared" si="1"/>
+        <v>BABOTO (200)</v>
+      </c>
+      <c r="O101" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S101" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="14">
         <v>61</v>
       </c>
@@ -5231,20 +5571,24 @@
       <c r="G102">
         <v>201</v>
       </c>
-      <c r="N102" s="11" t="s">
+      <c r="H102" t="str">
+        <f t="shared" si="1"/>
+        <v>SOUKOUTALIN (201)</v>
+      </c>
+      <c r="O102" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O102" s="3" t="s">
+      <c r="P102" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="Q102" s="3" t="s">
+      <c r="R102" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="R102" s="3" t="s">
+      <c r="S102" s="3" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="14">
         <v>62</v>
       </c>
@@ -5266,20 +5610,24 @@
       <c r="G103">
         <v>202</v>
       </c>
-      <c r="N103" s="13" t="s">
+      <c r="H103" t="str">
+        <f t="shared" si="1"/>
+        <v>KOKOLON (202)</v>
+      </c>
+      <c r="O103" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O103" s="3" t="s">
+      <c r="P103" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="Q103" s="3" t="s">
+      <c r="R103" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="R103" s="3" t="s">
+      <c r="S103" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="14">
         <v>63</v>
       </c>
@@ -5301,20 +5649,24 @@
       <c r="G104">
         <v>203</v>
       </c>
-      <c r="N104" s="13" t="s">
+      <c r="H104" t="str">
+        <f t="shared" si="1"/>
+        <v>SIKORONI (203)</v>
+      </c>
+      <c r="O104" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O104" s="3" t="s">
+      <c r="P104" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="Q104" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="R104" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S104" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="14">
         <v>64</v>
       </c>
@@ -5336,20 +5688,24 @@
       <c r="G105">
         <v>204</v>
       </c>
-      <c r="N105" s="13" t="s">
+      <c r="H105" t="str">
+        <f t="shared" si="1"/>
+        <v>BENDOUGOUNI (204)</v>
+      </c>
+      <c r="O105" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O105" s="3" t="s">
+      <c r="P105" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q105" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="R105" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S105" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="14">
         <v>65</v>
       </c>
@@ -5371,20 +5727,24 @@
       <c r="G106">
         <v>205</v>
       </c>
-      <c r="N106" s="13" t="s">
+      <c r="H106" t="str">
+        <f t="shared" si="1"/>
+        <v>BOUGARIBAYA (205)</v>
+      </c>
+      <c r="O106" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="O106" s="3" t="s">
+      <c r="P106" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="Q106" s="5" t="s">
+      <c r="R106" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="R106" s="3" t="s">
+      <c r="S106" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="14">
         <v>66</v>
       </c>
@@ -5406,20 +5766,24 @@
       <c r="G107">
         <v>206</v>
       </c>
-      <c r="N107" s="13" t="s">
+      <c r="H107" t="str">
+        <f t="shared" si="1"/>
+        <v>GONTAN (206)</v>
+      </c>
+      <c r="O107" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O107" s="3" t="s">
+      <c r="P107" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Q107" s="3" t="s">
+      <c r="R107" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="R107" s="3" t="s">
+      <c r="S107" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="14">
         <v>67</v>
       </c>
@@ -5441,20 +5805,24 @@
       <c r="G108">
         <v>207</v>
       </c>
-      <c r="N108" s="13" t="s">
+      <c r="H108" t="str">
+        <f t="shared" si="1"/>
+        <v>KITA GARE (207)</v>
+      </c>
+      <c r="O108" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O108" s="3" t="s">
+      <c r="P108" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="Q108" s="3" t="s">
+      <c r="R108" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="R108" s="3" t="s">
+      <c r="S108" s="3" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="14">
         <v>68</v>
       </c>
@@ -5476,20 +5844,24 @@
       <c r="G109">
         <v>208</v>
       </c>
-      <c r="N109" s="13" t="s">
+      <c r="H109" t="str">
+        <f t="shared" si="1"/>
+        <v>KONITONOMA DJEMAKANA (208)</v>
+      </c>
+      <c r="O109" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O109" s="3" t="s">
+      <c r="P109" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q109" s="5" t="s">
+      <c r="R109" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="R109" s="3" t="s">
+      <c r="S109" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="14">
         <v>69</v>
       </c>
@@ -5511,20 +5883,24 @@
       <c r="G110">
         <v>209</v>
       </c>
-      <c r="N110" s="13" t="s">
+      <c r="H110" t="str">
+        <f t="shared" si="1"/>
+        <v>KODOGONI (209)</v>
+      </c>
+      <c r="O110" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O110" s="3" t="s">
+      <c r="P110" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q110" s="3" t="s">
+      <c r="R110" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="R110" s="3" t="s">
+      <c r="S110" s="3" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="14">
         <v>70</v>
       </c>
@@ -5546,20 +5922,24 @@
       <c r="G111">
         <v>210</v>
       </c>
-      <c r="N111" s="13" t="s">
+      <c r="H111" t="str">
+        <f t="shared" si="1"/>
+        <v>DJABALA (210)</v>
+      </c>
+      <c r="O111" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O111" s="3" t="s">
+      <c r="P111" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="Q111" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="R111" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S111" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="14">
         <v>71</v>
       </c>
@@ -5581,20 +5961,24 @@
       <c r="G112">
         <v>211</v>
       </c>
-      <c r="N112" s="13" t="s">
+      <c r="H112" t="str">
+        <f t="shared" si="1"/>
+        <v>TOROLO (211)</v>
+      </c>
+      <c r="O112" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O112" s="3" t="s">
+      <c r="P112" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="Q112" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="R112" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="113" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S112" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="14">
         <v>72</v>
       </c>
@@ -5616,20 +6000,24 @@
       <c r="G113">
         <v>212</v>
       </c>
-      <c r="N113" s="13" t="s">
+      <c r="H113" t="str">
+        <f t="shared" si="1"/>
+        <v>KOBRI (212)</v>
+      </c>
+      <c r="O113" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O113" s="3" t="s">
+      <c r="P113" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="Q113" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="R113" s="3" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="114" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S113" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="14">
         <v>73</v>
       </c>
@@ -5651,20 +6039,24 @@
       <c r="G114">
         <v>213</v>
       </c>
-      <c r="N114" s="13" t="s">
+      <c r="H114" t="str">
+        <f t="shared" si="1"/>
+        <v>KALLA (213)</v>
+      </c>
+      <c r="O114" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O114" s="3" t="s">
+      <c r="P114" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="Q114" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="R114" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="115" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S114" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="14">
         <v>74</v>
       </c>
@@ -5686,20 +6078,24 @@
       <c r="G115">
         <v>214</v>
       </c>
-      <c r="N115" s="13" t="s">
+      <c r="H115" t="str">
+        <f t="shared" si="1"/>
+        <v>DALAMA (214)</v>
+      </c>
+      <c r="O115" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O115" s="3" t="s">
+      <c r="P115" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="Q115" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="R115" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="116" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S115" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="14">
         <v>75</v>
       </c>
@@ -5721,20 +6117,24 @@
       <c r="G116">
         <v>215</v>
       </c>
-      <c r="N116" s="20" t="s">
+      <c r="H116" t="str">
+        <f t="shared" si="1"/>
+        <v>FARÉNA (215)</v>
+      </c>
+      <c r="O116" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="O116" s="2" t="s">
+      <c r="P116" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="Q116" s="3" t="s">
+      <c r="R116" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="R116" s="3" t="s">
+      <c r="S116" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="14">
         <v>76</v>
       </c>
@@ -5756,20 +6156,24 @@
       <c r="G117">
         <v>216</v>
       </c>
-      <c r="N117" s="13" t="s">
+      <c r="H117" t="str">
+        <f t="shared" si="1"/>
+        <v>SAMEDOUGOU (216)</v>
+      </c>
+      <c r="O117" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O117" s="3" t="s">
+      <c r="P117" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="Q117" s="3" t="s">
+      <c r="R117" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R117" s="3" t="s">
+      <c r="S117" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="14">
         <v>77</v>
       </c>
@@ -5791,20 +6195,24 @@
       <c r="G118">
         <v>217</v>
       </c>
-      <c r="N118" s="13" t="s">
+      <c r="H118" t="str">
+        <f t="shared" si="1"/>
+        <v>BANKO (217)</v>
+      </c>
+      <c r="O118" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O118" s="3" t="s">
+      <c r="P118" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="Q118" s="3" t="s">
+      <c r="R118" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R118" s="3" t="s">
+      <c r="S118" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="14">
         <v>78</v>
       </c>
@@ -5826,20 +6234,24 @@
       <c r="G119">
         <v>218</v>
       </c>
-      <c r="N119" s="13" t="s">
+      <c r="H119" t="str">
+        <f t="shared" si="1"/>
+        <v>KOLFLO (218)</v>
+      </c>
+      <c r="O119" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O119" s="3" t="s">
+      <c r="P119" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="Q119" s="3" t="s">
+      <c r="R119" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="R119" s="3" t="s">
+      <c r="S119" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="14">
         <v>79</v>
       </c>
@@ -5861,20 +6273,24 @@
       <c r="G120">
         <v>219</v>
       </c>
-      <c r="N120" s="20" t="s">
+      <c r="H120" t="str">
+        <f t="shared" si="1"/>
+        <v>FIRIA (219)</v>
+      </c>
+      <c r="O120" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="O120" s="2" t="s">
+      <c r="P120" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="Q120" s="3" t="s">
+      <c r="R120" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="R120" s="3" t="s">
+      <c r="S120" s="3" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="14">
         <v>80</v>
       </c>
@@ -5896,20 +6312,24 @@
       <c r="G121">
         <v>220</v>
       </c>
-      <c r="N121" s="13" t="s">
+      <c r="H121" t="str">
+        <f t="shared" si="1"/>
+        <v>SANDIAMBOUGOU (220)</v>
+      </c>
+      <c r="O121" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O121" s="3" t="s">
+      <c r="P121" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="Q121" s="3" t="s">
+      <c r="R121" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="R121" s="3" t="s">
+      <c r="S121" s="3" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="14">
         <v>81</v>
       </c>
@@ -5931,20 +6351,24 @@
       <c r="G122">
         <v>221</v>
       </c>
-      <c r="N122" s="20" t="s">
+      <c r="H122" t="str">
+        <f t="shared" si="1"/>
+        <v>SÉBÉKORO (221)</v>
+      </c>
+      <c r="O122" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="O122" s="2" t="s">
+      <c r="P122" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="Q122" s="3" t="s">
+      <c r="R122" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="R122" s="3" t="s">
+      <c r="S122" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="14">
         <v>82</v>
       </c>
@@ -5966,20 +6390,24 @@
       <c r="G123">
         <v>222</v>
       </c>
-      <c r="N123" s="13" t="s">
+      <c r="H123" t="str">
+        <f t="shared" si="1"/>
+        <v>KOLAMINI (222)</v>
+      </c>
+      <c r="O123" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O123" s="3" t="s">
+      <c r="P123" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="Q123" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="R123" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="124" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S123" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="14">
         <v>83</v>
       </c>
@@ -6001,20 +6429,24 @@
       <c r="G124">
         <v>223</v>
       </c>
-      <c r="N124" s="20" t="s">
+      <c r="H124" t="str">
+        <f t="shared" si="1"/>
+        <v>MANAKO II (223)</v>
+      </c>
+      <c r="O124" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="O124" s="2" t="s">
+      <c r="P124" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="Q124" s="3" t="s">
+      <c r="R124" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="R124" s="3" t="s">
+      <c r="S124" s="3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="14">
         <v>84</v>
       </c>
@@ -6036,20 +6468,24 @@
       <c r="G125">
         <v>224</v>
       </c>
-      <c r="N125" s="13" t="s">
+      <c r="H125" t="str">
+        <f t="shared" si="1"/>
+        <v>BAYALA (224)</v>
+      </c>
+      <c r="O125" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O125" s="5" t="s">
+      <c r="P125" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Q125" s="3" t="s">
+      <c r="R125" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="R125" s="3" t="s">
+      <c r="S125" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="14">
         <v>85</v>
       </c>
@@ -6071,20 +6507,24 @@
       <c r="G126">
         <v>225</v>
       </c>
-      <c r="N126" s="13" t="s">
+      <c r="H126" t="str">
+        <f t="shared" si="1"/>
+        <v>SOURANZAN DALALA (225)</v>
+      </c>
+      <c r="O126" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O126" s="5" t="s">
+      <c r="P126" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="Q126" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="R126" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="127" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S126" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="14">
         <v>86</v>
       </c>
@@ -6106,20 +6546,24 @@
       <c r="G127">
         <v>226</v>
       </c>
-      <c r="N127" s="13" t="s">
+      <c r="H127" t="str">
+        <f t="shared" si="1"/>
+        <v>BADOUGOU (226)</v>
+      </c>
+      <c r="O127" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O127" s="5" t="s">
+      <c r="P127" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="Q127" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="R127" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="128" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S127" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="14">
         <v>87</v>
       </c>
@@ -6141,20 +6585,24 @@
       <c r="G128">
         <v>227</v>
       </c>
-      <c r="N128" s="20" t="s">
+      <c r="H128" t="str">
+        <f t="shared" si="1"/>
+        <v>DIALAKONI (227)</v>
+      </c>
+      <c r="O128" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O128" s="2" t="s">
+      <c r="P128" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="Q128" s="3" t="s">
+      <c r="R128" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="R128" s="3" t="s">
+      <c r="S128" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="14">
         <v>88</v>
       </c>
@@ -6176,20 +6624,24 @@
       <c r="G129">
         <v>228</v>
       </c>
-      <c r="N129" s="21" t="s">
+      <c r="H129" t="str">
+        <f t="shared" si="1"/>
+        <v>BARAKAYA (228)</v>
+      </c>
+      <c r="O129" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="O129" s="2" t="s">
+      <c r="P129" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="Q129" s="5" t="s">
+      <c r="R129" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="R129" s="5" t="s">
+      <c r="S129" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="14">
         <v>89</v>
       </c>
@@ -6211,20 +6663,24 @@
       <c r="G130">
         <v>229</v>
       </c>
-      <c r="N130" s="19" t="s">
+      <c r="H130" t="str">
+        <f t="shared" si="1"/>
+        <v>SAGABARI (229)</v>
+      </c>
+      <c r="O130" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="O130" s="19" t="s">
+      <c r="P130" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="Q130" s="11" t="s">
+      <c r="R130" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="R130" s="3" t="s">
+      <c r="S130" s="3" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="14">
         <v>90</v>
       </c>
@@ -6246,20 +6702,24 @@
       <c r="G131">
         <v>230</v>
       </c>
-      <c r="N131" s="20" t="s">
+      <c r="H131" t="str">
+        <f t="shared" ref="H131:H184" si="2">_xlfn.CONCAT(E131, " (", G131, ")")</f>
+        <v>DJOUGOUFING (230)</v>
+      </c>
+      <c r="O131" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O131" s="20" t="s">
+      <c r="P131" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="Q131" s="13" t="s">
+      <c r="R131" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="R131" s="3" t="s">
+      <c r="S131" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="14">
         <v>91</v>
       </c>
@@ -6281,20 +6741,24 @@
       <c r="G132">
         <v>231</v>
       </c>
-      <c r="N132" s="20" t="s">
+      <c r="H132" t="str">
+        <f t="shared" si="2"/>
+        <v>KOUNTOUGOU (231)</v>
+      </c>
+      <c r="O132" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O132" s="21" t="s">
+      <c r="P132" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="Q132" s="12" t="s">
+      <c r="R132" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="R132" s="3" t="s">
+      <c r="S132" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="14">
         <v>92</v>
       </c>
@@ -6316,20 +6780,24 @@
       <c r="G133">
         <v>232</v>
       </c>
-      <c r="N133" s="20" t="s">
+      <c r="H133" t="str">
+        <f t="shared" si="2"/>
+        <v>GAKROUKOTO (232)</v>
+      </c>
+      <c r="O133" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O133" s="19" t="s">
+      <c r="P133" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="Q133" s="11" t="s">
+      <c r="R133" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="R133" s="3" t="s">
+      <c r="S133" s="3" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="14">
         <v>93</v>
       </c>
@@ -6351,20 +6819,24 @@
       <c r="G134">
         <v>233</v>
       </c>
-      <c r="N134" s="20" t="s">
+      <c r="H134" t="str">
+        <f t="shared" si="2"/>
+        <v>LINGUEKOTO (233)</v>
+      </c>
+      <c r="O134" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O134" s="21" t="s">
+      <c r="P134" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="Q134" s="12" t="s">
+      <c r="R134" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="R134" s="3" t="s">
+      <c r="S134" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="14">
         <v>94</v>
       </c>
@@ -6386,20 +6858,24 @@
       <c r="G135">
         <v>234</v>
       </c>
-      <c r="N135" s="20" t="s">
+      <c r="H135" t="str">
+        <f t="shared" si="2"/>
+        <v>BALÉA (234)</v>
+      </c>
+      <c r="O135" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O135" s="19" t="s">
+      <c r="P135" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="Q135" s="11" t="s">
+      <c r="R135" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="R135" s="3" t="s">
+      <c r="S135" s="3" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="14">
         <v>95</v>
       </c>
@@ -6421,20 +6897,24 @@
       <c r="G136">
         <v>235</v>
       </c>
-      <c r="N136" s="20" t="s">
+      <c r="H136" t="str">
+        <f t="shared" si="2"/>
+        <v>KOURAGUÉ (235)</v>
+      </c>
+      <c r="O136" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O136" s="21" t="s">
+      <c r="P136" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="Q136" s="12" t="s">
+      <c r="R136" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="R136" s="3" t="s">
+      <c r="S136" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="14">
         <v>96</v>
       </c>
@@ -6456,20 +6936,24 @@
       <c r="G137">
         <v>236</v>
       </c>
-      <c r="N137" s="20" t="s">
+      <c r="H137" t="str">
+        <f t="shared" si="2"/>
+        <v>MATIRA (236)</v>
+      </c>
+      <c r="O137" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O137" s="2" t="s">
+      <c r="P137" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="Q137" s="3" t="s">
+      <c r="R137" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="R137" s="3" t="s">
+      <c r="S137" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="14">
         <v>97</v>
       </c>
@@ -6491,20 +6975,24 @@
       <c r="G138">
         <v>237</v>
       </c>
-      <c r="N138" s="20" t="s">
+      <c r="H138" t="str">
+        <f t="shared" si="2"/>
+        <v>KONKONIA (237)</v>
+      </c>
+      <c r="O138" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O138" s="19" t="s">
+      <c r="P138" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="Q138" s="11" t="s">
+      <c r="R138" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="R138" s="3" t="s">
+      <c r="S138" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="14">
         <v>98</v>
       </c>
@@ -6526,20 +7014,24 @@
       <c r="G139">
         <v>238</v>
       </c>
-      <c r="N139" s="20" t="s">
+      <c r="H139" t="str">
+        <f t="shared" si="2"/>
+        <v>GALLÉ (238)</v>
+      </c>
+      <c r="O139" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O139" s="21" t="s">
+      <c r="P139" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="Q139" s="12" t="s">
+      <c r="R139" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="R139" s="3" t="s">
+      <c r="S139" s="3" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="14">
         <v>99</v>
       </c>
@@ -6561,20 +7053,24 @@
       <c r="G140">
         <v>239</v>
       </c>
-      <c r="N140" s="20" t="s">
+      <c r="H140" t="str">
+        <f t="shared" si="2"/>
+        <v>SEGOUNA (239)</v>
+      </c>
+      <c r="O140" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O140" s="19" t="s">
+      <c r="P140" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="Q140" s="11" t="s">
+      <c r="R140" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="R140" s="3" t="s">
+      <c r="S140" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="14">
         <v>100</v>
       </c>
@@ -6596,20 +7092,24 @@
       <c r="G141">
         <v>240</v>
       </c>
-      <c r="N141" s="20" t="s">
+      <c r="H141" t="str">
+        <f t="shared" si="2"/>
+        <v>GALSINDÉ (240)</v>
+      </c>
+      <c r="O141" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O141" s="21" t="s">
+      <c r="P141" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="Q141" s="12" t="s">
+      <c r="R141" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="R141" s="3" t="s">
+      <c r="S141" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="14">
         <v>101</v>
       </c>
@@ -6631,20 +7131,24 @@
       <c r="G142">
         <v>241</v>
       </c>
-      <c r="N142" s="20" t="s">
+      <c r="H142" t="str">
+        <f t="shared" si="2"/>
+        <v>MALAKO (241)</v>
+      </c>
+      <c r="O142" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O142" s="2" t="s">
+      <c r="P142" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="Q142" s="3" t="s">
+      <c r="R142" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="R142" s="5" t="s">
+      <c r="S142" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="14">
         <v>102</v>
       </c>
@@ -6666,20 +7170,24 @@
       <c r="G143">
         <v>242</v>
       </c>
-      <c r="N143" s="20" t="s">
+      <c r="H143" t="str">
+        <f t="shared" si="2"/>
+        <v>FALOYA (242)</v>
+      </c>
+      <c r="O143" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O143" s="2" t="s">
+      <c r="P143" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="Q143" s="3" t="s">
+      <c r="R143" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R143" s="3" t="s">
+      <c r="S143" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="14">
         <v>103</v>
       </c>
@@ -6701,20 +7209,24 @@
       <c r="G144">
         <v>243</v>
       </c>
-      <c r="N144" s="21" t="s">
+      <c r="H144" t="str">
+        <f t="shared" si="2"/>
+        <v>BAGUITA (243)</v>
+      </c>
+      <c r="O144" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="O144" s="2" t="s">
+      <c r="P144" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="Q144" s="3" t="s">
+      <c r="R144" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R144" s="3" t="s">
+      <c r="S144" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="14">
         <v>104</v>
       </c>
@@ -6736,20 +7248,24 @@
       <c r="G145">
         <v>244</v>
       </c>
-      <c r="N145" s="19" t="s">
+      <c r="H145" t="str">
+        <f t="shared" si="2"/>
+        <v>SÉFETO (244)</v>
+      </c>
+      <c r="O145" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="O145" s="19" t="s">
+      <c r="P145" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="Q145" s="11" t="s">
+      <c r="R145" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="R145" s="3" t="s">
+      <c r="S145" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="14">
         <v>105</v>
       </c>
@@ -6771,20 +7287,24 @@
       <c r="G146">
         <v>245</v>
       </c>
-      <c r="N146" s="20" t="s">
+      <c r="H146" t="str">
+        <f t="shared" si="2"/>
+        <v>KAREGA (245)</v>
+      </c>
+      <c r="O146" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O146" s="21" t="s">
+      <c r="P146" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="Q146" s="12" t="s">
+      <c r="R146" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="R146" s="3" t="s">
+      <c r="S146" s="3" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="14">
         <v>106</v>
       </c>
@@ -6806,20 +7326,24 @@
       <c r="G147">
         <v>246</v>
       </c>
-      <c r="N147" s="20" t="s">
+      <c r="H147" t="str">
+        <f t="shared" si="2"/>
+        <v>GUEMOUKOURABA (246)</v>
+      </c>
+      <c r="O147" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O147" s="19" t="s">
+      <c r="P147" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="Q147" s="11" t="s">
+      <c r="R147" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="R147" s="3" t="s">
+      <c r="S147" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="14">
         <v>107</v>
       </c>
@@ -6841,20 +7365,24 @@
       <c r="G148">
         <v>247</v>
       </c>
-      <c r="N148" s="20" t="s">
+      <c r="H148" t="str">
+        <f t="shared" si="2"/>
+        <v>GUESSÉBINE (247)</v>
+      </c>
+      <c r="O148" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O148" s="21" t="s">
+      <c r="P148" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="Q148" s="12" t="s">
+      <c r="R148" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="R148" s="3" t="s">
+      <c r="S148" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="14">
         <v>108</v>
       </c>
@@ -6876,20 +7404,24 @@
       <c r="G149">
         <v>248</v>
       </c>
-      <c r="N149" s="20" t="s">
+      <c r="H149" t="str">
+        <f t="shared" si="2"/>
+        <v>KAGORO-MOUNTAN (248)</v>
+      </c>
+      <c r="O149" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O149" s="19" t="s">
+      <c r="P149" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="Q149" s="11" t="s">
+      <c r="R149" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="R149" s="3" t="s">
+      <c r="S149" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="14">
         <v>109</v>
       </c>
@@ -6911,20 +7443,24 @@
       <c r="G150">
         <v>249</v>
       </c>
-      <c r="N150" s="20" t="s">
+      <c r="H150" t="str">
+        <f t="shared" si="2"/>
+        <v>GARANGOU (249)</v>
+      </c>
+      <c r="O150" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O150" s="21" t="s">
+      <c r="P150" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="Q150" s="12" t="s">
+      <c r="R150" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="R150" s="3" t="s">
+      <c r="S150" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="14">
         <v>110</v>
       </c>
@@ -6946,20 +7482,24 @@
       <c r="G151">
         <v>250</v>
       </c>
-      <c r="N151" s="20" t="s">
+      <c r="H151" t="str">
+        <f t="shared" si="2"/>
+        <v>DJOUGOUNTÉ (250)</v>
+      </c>
+      <c r="O151" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O151" s="2" t="s">
+      <c r="P151" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="Q151" s="5" t="s">
+      <c r="R151" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="R151" s="5" t="s">
+      <c r="S151" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="14">
         <v>111</v>
       </c>
@@ -6981,20 +7521,24 @@
       <c r="G152">
         <v>251</v>
       </c>
-      <c r="N152" s="20" t="s">
+      <c r="H152" t="str">
+        <f t="shared" si="2"/>
+        <v>NAFADJI (251)</v>
+      </c>
+      <c r="O152" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="O152" s="2" t="s">
+      <c r="P152" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="Q152" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="R152" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="153" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S152" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="14">
         <v>112</v>
       </c>
@@ -7016,16 +7560,20 @@
       <c r="G153">
         <v>252</v>
       </c>
-      <c r="N153" s="20"/>
-      <c r="O153" s="2"/>
-      <c r="Q153" s="3" t="s">
+      <c r="H153" t="str">
+        <f t="shared" si="2"/>
+        <v>SIRAMISSÉ (252)</v>
+      </c>
+      <c r="O153" s="20"/>
+      <c r="P153" s="2"/>
+      <c r="R153" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="R153" s="3" t="s">
+      <c r="S153" s="3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="14">
         <v>113</v>
       </c>
@@ -7047,14 +7595,18 @@
       <c r="G154">
         <v>253</v>
       </c>
-      <c r="Q154" s="11" t="s">
+      <c r="H154" t="str">
+        <f t="shared" si="2"/>
+        <v>DJOUGOUN (253)</v>
+      </c>
+      <c r="R154" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="R154" s="3" t="s">
+      <c r="S154" s="3" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="14">
         <v>114</v>
       </c>
@@ -7076,14 +7628,18 @@
       <c r="G155">
         <v>254</v>
       </c>
-      <c r="Q155" s="12" t="s">
+      <c r="H155" t="str">
+        <f t="shared" si="2"/>
+        <v>KOBOKOTO (254)</v>
+      </c>
+      <c r="R155" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="R155" s="5" t="s">
+      <c r="S155" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="14">
         <v>115</v>
       </c>
@@ -7105,14 +7661,18 @@
       <c r="G156">
         <v>255</v>
       </c>
-      <c r="Q156" s="11" t="s">
+      <c r="H156" t="str">
+        <f t="shared" si="2"/>
+        <v>KENIENINFE (255)</v>
+      </c>
+      <c r="R156" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="R156" s="3" t="s">
+      <c r="S156" s="3" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="14">
         <v>116</v>
       </c>
@@ -7134,14 +7694,18 @@
       <c r="G157">
         <v>256</v>
       </c>
-      <c r="Q157" s="12" t="s">
+      <c r="H157" t="str">
+        <f t="shared" si="2"/>
+        <v>DALABA (256)</v>
+      </c>
+      <c r="R157" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="R157" s="3" t="s">
+      <c r="S157" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="14">
         <v>117</v>
       </c>
@@ -7163,14 +7727,18 @@
       <c r="G158">
         <v>257</v>
       </c>
-      <c r="Q158" s="11" t="s">
+      <c r="H158" t="str">
+        <f t="shared" si="2"/>
+        <v>NIAGANÉ (257)</v>
+      </c>
+      <c r="R158" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="R158" s="3" t="s">
+      <c r="S158" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="14">
         <v>118</v>
       </c>
@@ -7192,14 +7760,18 @@
       <c r="G159">
         <v>258</v>
       </c>
-      <c r="Q159" s="16" t="s">
+      <c r="H159" t="str">
+        <f t="shared" si="2"/>
+        <v>NÈGUÈBOUGOU (258)</v>
+      </c>
+      <c r="R159" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="R159" s="5" t="s">
+      <c r="S159" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="14">
         <v>119</v>
       </c>
@@ -7221,14 +7793,18 @@
       <c r="G160">
         <v>259</v>
       </c>
-      <c r="Q160" s="3" t="s">
+      <c r="H160" t="str">
+        <f t="shared" si="2"/>
+        <v>BANDIOUGOULA (259)</v>
+      </c>
+      <c r="R160" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="R160" s="5" t="s">
+      <c r="S160" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="14">
         <v>120</v>
       </c>
@@ -7250,14 +7826,18 @@
       <c r="G161">
         <v>260</v>
       </c>
-      <c r="Q161" s="3" t="s">
+      <c r="H161" t="str">
+        <f t="shared" si="2"/>
+        <v>BOUGOUDÉRÉ (260)</v>
+      </c>
+      <c r="R161" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="R161" s="3" t="s">
+      <c r="S161" s="3" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="14">
         <v>121</v>
       </c>
@@ -7279,14 +7859,18 @@
       <c r="G162">
         <v>261</v>
       </c>
-      <c r="Q162" s="3" t="s">
+      <c r="H162" t="str">
+        <f t="shared" si="2"/>
+        <v>BENA FADJIGUILA (261)</v>
+      </c>
+      <c r="R162" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="R162" s="3" t="s">
+      <c r="S162" s="3" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="14">
         <v>122</v>
       </c>
@@ -7308,14 +7892,18 @@
       <c r="G163">
         <v>262</v>
       </c>
-      <c r="Q163" s="3" t="s">
-        <v>134</v>
+      <c r="H163" t="str">
+        <f t="shared" si="2"/>
+        <v>NIAGNELA (262)</v>
       </c>
       <c r="R163" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="164" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S163" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="14">
         <v>123</v>
       </c>
@@ -7337,14 +7925,18 @@
       <c r="G164">
         <v>263</v>
       </c>
-      <c r="Q164" s="3" t="s">
+      <c r="H164" t="str">
+        <f t="shared" si="2"/>
+        <v>DIABOUGOU (263)</v>
+      </c>
+      <c r="R164" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R164" s="3" t="s">
+      <c r="S164" s="3" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="14">
         <v>124</v>
       </c>
@@ -7366,14 +7958,18 @@
       <c r="G165">
         <v>264</v>
       </c>
-      <c r="Q165" s="3" t="s">
-        <v>96</v>
+      <c r="H165" t="str">
+        <f t="shared" si="2"/>
+        <v>TONGO (264)</v>
       </c>
       <c r="R165" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="166" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S165" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="14">
         <v>125</v>
       </c>
@@ -7395,14 +7991,18 @@
       <c r="G166">
         <v>265</v>
       </c>
-      <c r="Q166" s="3" t="s">
-        <v>73</v>
+      <c r="H166" t="str">
+        <f t="shared" si="2"/>
+        <v>GORY (265)</v>
       </c>
       <c r="R166" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="167" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S166" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="14">
         <v>126</v>
       </c>
@@ -7424,14 +8024,18 @@
       <c r="G167">
         <v>266</v>
       </c>
-      <c r="Q167" s="3" t="s">
+      <c r="H167" t="str">
+        <f t="shared" si="2"/>
+        <v>HAMDALLAYE (266)</v>
+      </c>
+      <c r="R167" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="R167" s="3" t="s">
+      <c r="S167" s="3" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="14">
         <v>127</v>
       </c>
@@ -7453,14 +8057,18 @@
       <c r="G168">
         <v>267</v>
       </c>
-      <c r="Q168" s="3" t="s">
+      <c r="H168" t="str">
+        <f t="shared" si="2"/>
+        <v>KOMODINDI (267)</v>
+      </c>
+      <c r="R168" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="R168" s="3" t="s">
+      <c r="S168" s="3" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="14">
         <v>128</v>
       </c>
@@ -7482,14 +8090,18 @@
       <c r="G169">
         <v>268</v>
       </c>
-      <c r="Q169" s="3" t="s">
+      <c r="H169" t="str">
+        <f t="shared" si="2"/>
+        <v>MANTHIA (268)</v>
+      </c>
+      <c r="R169" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="R169" s="3" t="s">
+      <c r="S169" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="14">
         <v>129</v>
       </c>
@@ -7511,14 +8123,18 @@
       <c r="G170">
         <v>269</v>
       </c>
-      <c r="Q170" s="3" t="s">
+      <c r="H170" t="str">
+        <f t="shared" si="2"/>
+        <v>KIRANE (269)</v>
+      </c>
+      <c r="R170" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="R170" s="3" t="s">
+      <c r="S170" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="14">
         <v>130</v>
       </c>
@@ -7540,14 +8156,18 @@
       <c r="G171">
         <v>270</v>
       </c>
-      <c r="Q171" s="3" t="s">
+      <c r="H171" t="str">
+        <f t="shared" si="2"/>
+        <v>KODJÉ (270)</v>
+      </c>
+      <c r="R171" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="R171" s="3" t="s">
+      <c r="S171" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="14">
         <v>131</v>
       </c>
@@ -7569,14 +8189,18 @@
       <c r="G172">
         <v>271</v>
       </c>
-      <c r="Q172" s="3" t="s">
+      <c r="H172" t="str">
+        <f t="shared" si="2"/>
+        <v>KORAMPO (271)</v>
+      </c>
+      <c r="R172" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="R172" s="3" t="s">
+      <c r="S172" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="14">
         <v>132</v>
       </c>
@@ -7598,14 +8222,18 @@
       <c r="G173">
         <v>272</v>
       </c>
-      <c r="Q173" s="3" t="s">
-        <v>38</v>
+      <c r="H173" t="str">
+        <f t="shared" si="2"/>
+        <v>SÉNÉ WALY DIALOUBÉ (272)</v>
       </c>
       <c r="R173" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="174" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S173" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="14">
         <v>133</v>
       </c>
@@ -7627,14 +8255,18 @@
       <c r="G174">
         <v>273</v>
       </c>
-      <c r="Q174" s="3" t="s">
+      <c r="H174" t="str">
+        <f t="shared" si="2"/>
+        <v>LAKANGUEMOU (273)</v>
+      </c>
+      <c r="R174" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="R174" s="3" t="s">
+      <c r="S174" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="14">
         <v>134</v>
       </c>
@@ -7656,14 +8288,18 @@
       <c r="G175">
         <v>274</v>
       </c>
-      <c r="Q175" s="3" t="s">
+      <c r="H175" t="str">
+        <f t="shared" si="2"/>
+        <v>MARENA (274)</v>
+      </c>
+      <c r="R175" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="R175" s="3" t="s">
+      <c r="S175" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="14">
         <v>135</v>
       </c>
@@ -7685,14 +8321,18 @@
       <c r="G176">
         <v>275</v>
       </c>
-      <c r="Q176" s="3" t="s">
+      <c r="H176" t="str">
+        <f t="shared" si="2"/>
+        <v>NIOGOMÉRA (275)</v>
+      </c>
+      <c r="R176" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R176" s="3" t="s">
+      <c r="S176" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="14">
         <v>136</v>
       </c>
@@ -7714,14 +8354,18 @@
       <c r="G177">
         <v>276</v>
       </c>
-      <c r="Q177" s="3" t="s">
+      <c r="H177" t="str">
+        <f t="shared" si="2"/>
+        <v>GUIFFI (276)</v>
+      </c>
+      <c r="R177" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R177" s="3" t="s">
+      <c r="S177" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="14">
         <v>137</v>
       </c>
@@ -7743,14 +8387,18 @@
       <c r="G178">
         <v>277</v>
       </c>
-      <c r="Q178" s="3" t="s">
+      <c r="H178" t="str">
+        <f t="shared" si="2"/>
+        <v>NIAGNELA (TAGABA) (277)</v>
+      </c>
+      <c r="R178" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="R178" s="3" t="s">
+      <c r="S178" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="14">
         <v>138</v>
       </c>
@@ -7772,14 +8420,18 @@
       <c r="G179">
         <v>278</v>
       </c>
-      <c r="Q179" s="3" t="s">
+      <c r="H179" t="str">
+        <f t="shared" si="2"/>
+        <v>GUIDÉOURÉ (278)</v>
+      </c>
+      <c r="R179" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R179" s="3" t="s">
+      <c r="S179" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="14">
         <v>139</v>
       </c>
@@ -7801,14 +8453,18 @@
       <c r="G180">
         <v>279</v>
       </c>
-      <c r="Q180" s="3" t="s">
-        <v>32</v>
+      <c r="H180" t="str">
+        <f t="shared" si="2"/>
+        <v>YAGUINE (279)</v>
       </c>
       <c r="R180" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="181" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S180" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="14">
         <v>140</v>
       </c>
@@ -7830,14 +8486,18 @@
       <c r="G181">
         <v>280</v>
       </c>
-      <c r="Q181" s="3" t="s">
-        <v>158</v>
+      <c r="H181" t="str">
+        <f t="shared" si="2"/>
+        <v>DIADJI (280)</v>
       </c>
       <c r="R181" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="182" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S181" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="14">
         <v>141</v>
       </c>
@@ -7859,14 +8519,18 @@
       <c r="G182">
         <v>281</v>
       </c>
-      <c r="Q182" s="3" t="s">
+      <c r="H182" t="str">
+        <f t="shared" si="2"/>
+        <v>DIALAKA (281)</v>
+      </c>
+      <c r="R182" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="R182" s="3" t="s">
+      <c r="S182" s="3" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="14">
         <v>142</v>
       </c>
@@ -7888,14 +8552,18 @@
       <c r="G183">
         <v>282</v>
       </c>
-      <c r="Q183" s="3" t="s">
+      <c r="H183" t="str">
+        <f t="shared" si="2"/>
+        <v>LAMBATRA (282)</v>
+      </c>
+      <c r="R183" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R183" s="3" t="s">
+      <c r="S183" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="14">
         <v>143</v>
       </c>
@@ -7917,29 +8585,33 @@
       <c r="G184">
         <v>283</v>
       </c>
-      <c r="Q184" s="3" t="s">
-        <v>41</v>
+      <c r="H184" t="str">
+        <f t="shared" si="2"/>
+        <v>SAMBAGA (283)</v>
       </c>
       <c r="R184" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="S184" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F184" xr:uid="{02802C9A-C9ED-44E1-BBDB-EA690037CB45}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="Q2:R184">
-    <sortCondition ref="Q2:Q184"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S184">
     <sortCondition ref="R2:R184"/>
+    <sortCondition ref="S2:S184"/>
   </sortState>
-  <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O153 O190:O1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  <conditionalFormatting sqref="P1:P153 P190:P1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576 G1">
+  <conditionalFormatting sqref="E1:E1048576 G1:H1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1048576">
+  <conditionalFormatting sqref="S1:S1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
